--- a/output/pdf_financials_xlsx/CBA.xlsx
+++ b/output/pdf_financials_xlsx/CBA.xlsx
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.0581</v>
+        <v>-1.431848</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.166905</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.744974</v>
+        <v>-0.744974</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>1.562764</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.744974</v>
+        <v>-0.744974</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.562764</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-24.832467</v>
+        <v>24.832467</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-31.25528</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>8.458611040744008</v>
+        <v>208.458611040744</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>11.95715326548025</v>
@@ -6153,7 +6153,7 @@
         <v>-0.035527</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.054825</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -7777,52 +7777,52 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.169844</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.604423</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.156734</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.006395</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.053424</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.00325</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002582</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>-0.331576</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>-0.697547</v>
+        <v>-0.5210399999999999</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>2.158697</v>
+        <v>1.732353</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.024224</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.055693</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06795900000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009332</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009715</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
     </row>
     <row r="119">
@@ -12636,7 +12636,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -15724,7 +15728,11 @@
           <t>Fair value reserve</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -20636,7 +20644,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -26250,7 +26262,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -56518,10 +56534,10 @@
         </is>
       </c>
       <c r="E457" s="5" t="n">
-        <v>0.744974</v>
+        <v>-0.744974</v>
       </c>
       <c r="F457" s="5" t="n">
-        <v>1.508817</v>
+        <v>-1.508817</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CBA.xlsx
+++ b/output/pdf_financials_xlsx/CBA.xlsx
@@ -2584,19 +2584,19 @@
         <v>0.003458</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.0006310000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.005085</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.004549</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.000788</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.003355</v>
       </c>
     </row>
     <row r="35">
@@ -2706,19 +2706,19 @@
         <v>0.003458</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.0006310000000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.005085</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.004549</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.000788</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.003355</v>
       </c>
     </row>
     <row r="37">
@@ -3438,19 +3438,19 @@
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.0006310000000000001</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.015085</v>
+        <v>0.01</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.014549</v>
+        <v>0.01</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.010788</v>
+        <v>0.01</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.013355</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="49">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -50544,7 +50544,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E400" s="5" t="n">

--- a/output/pdf_financials_xlsx/CBA.xlsx
+++ b/output/pdf_financials_xlsx/CBA.xlsx
@@ -6764,28 +6764,28 @@
         <v>-0.006099</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>-0.075102</v>
+        <v>-0.052157</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.050558</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.013262</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010759</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.008798</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000172</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003298</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002546</v>
       </c>
     </row>
     <row r="102">
@@ -20052,7 +20052,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -23006,7 +23010,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -35160,7 +35168,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -37914,7 +37926,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E279" s="5" t="n">
         <v>0.0581</v>
       </c>
